--- a/data/seed/portfolio/L-2024-6498/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6498/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,21 +542,21 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>17764000</v>
+        <v>20522000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Mehnat Polimer AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>267971999</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000223993595001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №132/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №120/26, НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>272264000</v>
+        <v>275022000</v>
       </c>
     </row>
     <row r="9">
@@ -582,35 +582,35 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>14490000</v>
+        <v>7955000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2661 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №257/26, QQS 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>286754000</v>
+        <v>282977000</v>
       </c>
     </row>
     <row r="10">
@@ -622,21 +622,21 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>7694000</v>
+        <v>141538000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,152 +646,152 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5329 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8239 за поставленный товар</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>294448000</v>
+        <v>424515000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46208</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>61200000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>10740000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6498)</t>
+          <t>Omad Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>349173772</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16307000285424850417</t>
+          <t>20208000412269869001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6498 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №184/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>233248000</v>
+        <v>435255000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>58339000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>40838000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №31/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №281/26 от 03.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>291587000</v>
+        <v>394417000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>7402000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>349208000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Afrosiyob Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>377315002</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000258561180001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9398 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3939</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>298989000</v>
+        <v>45209000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28268000</v>
+        <v>61200000</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>363744948</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6498)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>16307000285424850417</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -801,11 +801,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1211</t>
+          <t>Kredit shartnomasi L-2024-6498 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>270721000</v>
+        <v>-15991000</v>
       </c>
     </row>
     <row r="15">
@@ -815,218 +815,218 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>87597000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>186287000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Saodat Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>183124000</v>
+        <v>170296000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>43804000</v>
+        <v>51718000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №83/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №165/26, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>226928000</v>
+        <v>222014000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>11217000</v>
+        <v>6788000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saodat Moy MChJ</t>
+          <t>Mehnat Polimer AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>315491737</t>
+          <t>267971999</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000264122698001</t>
+          <t>20208000223993595001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6796 от 08.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9467 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>238145000</v>
+        <v>228802000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9743000</v>
+        <v>87597000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>267482320</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000975515929001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №72/25</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>228402000</v>
+        <v>141205000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>15460000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>18538000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Marg'ilon Mato XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>307201695</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000447921133001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №22/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №12/26 от 07.07.2026</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>212942000</v>
+        <v>159743000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>103402000</v>
+        <v>18402000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1036,77 +1036,77 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №21/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №54/26, НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>316344000</v>
+        <v>178145000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>19775000</v>
+        <v>11138000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №97/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №191/26 от 07.07.2026</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>336119000</v>
+        <v>189283000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>11436000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>181337000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3243 от 10.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №872</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>347555000</v>
+        <v>7946000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>32539000</v>
+        <v>73988000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9637 13.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №6663 за поставленный товар</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>380094000</v>
+        <v>81934000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>22890000</v>
+        <v>9511000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saodat Moy MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>315491737</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000264122698001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1196,117 +1196,117 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №4924 за поставленный товар</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>402984000</v>
+        <v>91445000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>17187000</v>
+        <v>8948000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4631 13.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №3354 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>420171000</v>
+        <v>100393000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>16777000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>9743000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>254594097</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000471190172001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №119/26, НДС 12%</t>
+          <t>Аренда помещения за июль, дог. №33/25</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>436948000</v>
+        <v>90650000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>16315000</v>
+        <v>18358000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,37 +1316,37 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №166/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>453263000</v>
+        <v>109008000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>12625000</v>
+        <v>6834000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1356,51 +1356,51 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №239/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №4769 за поставленный товар</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>465888000</v>
+        <v>115842000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>9149000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>46431000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Farovon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>282320397</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000515929176001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1305 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №176/26</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>475037000</v>
+        <v>69411000</v>
       </c>
     </row>
     <row r="30">
@@ -1412,101 +1412,101 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>7766000</v>
+        <v>34366000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №57/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>482803000</v>
+        <v>103777000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>18907000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>24438000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>380679719</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000922239935001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №114/26 от 14.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2118</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>463896000</v>
+        <v>128215000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>10833000</v>
+        <v>19454000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,171 +1516,171 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2216 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №271/26, НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>474729000</v>
+        <v>147669000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>11945000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>15148000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Оплата за продукцию по договору №7/26, НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>462784000</v>
+        <v>162817000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>11945000</v>
+        <v>66126000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>231937806</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000819152950001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>Предоплата за материалы по договору №128/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>450839000</v>
+        <v>96691000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>13134000</v>
+        <v>25571000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №84/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №2/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>463973000</v>
+        <v>122262000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>11198000</v>
+        <v>17452000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2930 от 16.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №284/26, НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>475171000</v>
+        <v>139714000</v>
       </c>
     </row>
     <row r="37">
@@ -1690,157 +1690,157 @@
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>9139000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>9919000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8524</t>
+          <t>Оплата за продукцию по договору №68/26, НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>466032000</v>
+        <v>149633000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>65474000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>11945000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1281 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>531506000</v>
+        <v>137688000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>130148000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>11945000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1564 за поставленный товар</t>
+          <t>Налог н доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>661654000</v>
+        <v>125743000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>57757000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>83452000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saodat Moy MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>315491737</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000264122698001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9412 за поставленный товар</t>
+          <t>Оплата за сырье по договору №41/26 от 16.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>719411000</v>
+        <v>42291000</v>
       </c>
     </row>
     <row r="41">
@@ -1852,35 +1852,35 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>29619000</v>
+        <v>59026000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Xiva Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>225133083</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000776683359001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4130 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №146/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>749030000</v>
+        <v>101317000</v>
       </c>
     </row>
     <row r="42">
@@ -1892,101 +1892,101 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>28275000</v>
+        <v>10212000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1016 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №9432 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>777305000</v>
+        <v>111529000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>11478000</v>
+        <v>26325000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №284/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>788783000</v>
+        <v>137854000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>8924000</v>
+        <v>25544000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1996,256 +1996,256 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №230/26 от 20.07.2026</t>
+          <t>Предоплата за товар по дог. №29/26 от 22.07.2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>797707000</v>
+        <v>163398000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>754228000</v>
+        <v>15741000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №64/26 от 20.07.2026, НДС 12%</t>
+          <t>НДС ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>43479000</v>
+        <v>147657000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>31409000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>75104000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Nukus Polimer MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №207/26 от 22.07.2026</t>
+          <t>Оплата за сырье по договору №297/26 от 23.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>74888000</v>
+        <v>72553000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>14602000</v>
+        <v>106132000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3071 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №74/26, НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>89490000</v>
+        <v>178685000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>15912000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>20141000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №48/26, НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>73578000</v>
+        <v>198826000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>29031000</v>
+        <v>52646000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5883 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9111 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>102609000</v>
+        <v>251472000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>9105000</v>
+        <v>11797000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bekobod Avto Savdo MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>390329013</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000643988360001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №78/26 от 23.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №240/26, QQS 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>111714000</v>
+        <v>263269000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000760984131001</t>
+          <t>20208000427440373001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2280,113 +2280,113 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>105624000</v>
+        <v>257179000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>113002000</v>
+        <v>36623000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №197/26 от 23.07.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3178</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-7378000</v>
+        <v>220556000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>159591000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>53691000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Farovon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>282320397</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000515929176001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №227/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №2513</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>152213000</v>
+        <v>166865000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>30850000</v>
+        <v>53908000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,197 +2396,197 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №252/26</t>
+          <t>Оплата за транспортные услуги по дог. №41/26</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>121363000</v>
+        <v>112957000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>61798000</v>
+        <v>27844000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saodat Moy MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>315491737</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000264122698001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4733</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №239/26 ОТ 28.07.2026</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>183161000</v>
+        <v>140801000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>34185000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>112549000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Nukus Polimer MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3504 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4847</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>217346000</v>
+        <v>28252000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>16398000</v>
+        <v>26105000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №281/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №140/26, НДС 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>233744000</v>
+        <v>54357000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>13492000</v>
+        <v>200463000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7833 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №6057 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>247236000</v>
+        <v>254820000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>13311000</v>
+        <v>7933000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2596,197 +2596,187 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №270/26 от 27.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №9442 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>260547000</v>
+        <v>262753000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>8270000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>206562717</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3529 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>268817000</v>
+        <v>262453000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>30138000</v>
+        <v>121302000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Plastik MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>357676744</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000605527524001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №177/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3383 за поставленный товар</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>298955000</v>
+        <v>383755000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>14605000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>35668000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7243 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6060</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>313560000</v>
+        <v>348087000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>15523000</v>
+        <v>75422000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Navoiy Mehmonxona MChJ</t>
+          <t>Nukus Polimer MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>299507777</t>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000210026236001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №147/26</t>
+          <t>Оплата за товары согласно счет-фактуре №1289</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>298037000</v>
+        <v>272665000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>29555000</v>
+        <v>82359000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>363744948</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2796,157 +2786,152 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5536</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>268482000</v>
+        <v>190306000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>34649000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>22857000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №91/26</t>
+          <t>Оплата за товар по счет-фактуре №1978 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>233833000</v>
+        <v>213163000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>60588000</v>
+        <v>6919000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bekobod Avto Savdo MChJ</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>390329013</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000643988360001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3469 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №8002 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>294421000</v>
+        <v>220082000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>17834000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>61200000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>206562717</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6498)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>16307000285424850417</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №677 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-6498 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>312255000</v>
+        <v>158882000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>14218000</v>
+        <v>6379000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2956,192 +2941,197 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4179 от 31.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №158/26 от 07.08.2026</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>326473000</v>
+        <v>165261000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>63397000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Nurafshon Agro AJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата по счет-фактуре №6748 за поставленный товар</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>326173000</v>
+        <v>228658000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>9038000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>21298000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Navoiy Mehmonxona MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>299507777</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000210026236001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №906</t>
+          <t>Оплата за продукцию по договору №91/26, НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>317135000</v>
+        <v>249956000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>15793000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>16263000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Navoiy Mehmonxona MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>299507777</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000210026236001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №21/26</t>
+          <t>Оплата за товар по с/ф №8424 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>301342000</v>
+        <v>266219000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>16714000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>13669000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Marg'ilon Mato XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>307201695</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000447921133001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3316</t>
+          <t>Оплата за продукцию по договору №5/26, НДС 12%</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>284628000</v>
+        <v>279888000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>24616000</v>
+        <v>13052000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3151,152 +3141,157 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9262 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №112/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>309244000</v>
+        <v>292940000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>167646000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>6789000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №51/26 от 03.08.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8201</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>141598000</v>
+        <v>299729000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>41823000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>9161000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>254594097</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000471190172001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №170 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Арендная плата за август 2026 г. по договору №33/25</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>183421000</v>
+        <v>290568000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>14127000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>10482000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №189/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>197548000</v>
+        <v>280086000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>61200000</v>
+        <v>13857000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6498)</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>16307000285424850417</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3306,672 +3301,677 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6498 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за упаковочные материалы, с/ф №1159</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>136348000</v>
+        <v>266229000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>327132000</v>
+        <v>42605000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Farovon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>282320397</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000515929176001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8736</t>
+          <t>Предоплата за материалы по договору №8/26</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>-190784000</v>
+        <v>223624000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>74239000</v>
+        <v>11858000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8502 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3432 от 11.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-116545000</v>
+        <v>235482000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>40382000</v>
+        <v>18077000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2049 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №7465 за поставленный товар</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-76163000</v>
+        <v>253559000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>39974000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>50792000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6496 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по дог. №33/26</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>-36189000</v>
+        <v>202767000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>34667000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>19039000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>380679719</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000922239935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дг. №127/26 от 06.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №175/26, QQS 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>-70856000</v>
+        <v>221806000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>56514000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>25616000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №150/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1926 14.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>-127370000</v>
+        <v>247422000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>82359000</v>
+        <v>46450000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Nukus Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №6011</t>
+          <t>Оплата за товары согласно с/ф №4163</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>-209729000</v>
+        <v>200972000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>300124000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>11231000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №286 за поставленный товар</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>90395000</v>
+        <v>189741000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>17948000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>11231000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bekobod Avto Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>390329013</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000643988360001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №626 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>108343000</v>
+        <v>178510000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>15816000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>38535000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Afrosiyob Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>377315002</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000258561180001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1401 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №89/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>124159000</v>
+        <v>139975000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>9161000</v>
+        <v>92564000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>267482320</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000975515929001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №72/25</t>
+          <t>Оплата за транспортные услуги по договору №241/26</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>114998000</v>
+        <v>47411000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>51365000</v>
+        <v>48271000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №65/26 от 10.08.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №281/26</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>63633000</v>
+        <v>-860000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>53909000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>500544000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Bog'ishamol Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>291382543</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000977710952001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2898</t>
+          <t>Предоплат за товар по договору №126/26 от 20.08.2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>9724000</v>
+        <v>499684000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>37371000</v>
+        <v>49929000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2988 за поставленный товар</t>
+          <t>Tovar uchun to'lov, h/f №1219 20.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>47095000</v>
+        <v>549613000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>19193000</v>
+        <v>24598000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1604 от 13.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7098 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>66288000</v>
+        <v>574211000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>15757000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>46656000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3017 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №170/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>82045000</v>
+        <v>527555000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>40466000</v>
+        <v>55108000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3981,357 +3981,357 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9590 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3918</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>122511000</v>
+        <v>582663000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>10857000</v>
+        <v>23867000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9519 за поставленный товар</t>
+          <t>Предоплата за товар по договору №228/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>133368000</v>
+        <v>606530000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>26108000</v>
+        <v>23841000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2165 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>159476000</v>
+        <v>630371000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>11231000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>21131000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Предоплата за товар по договору №195/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>148245000</v>
+        <v>651502000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>11231000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>12613000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6000</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>137014000</v>
+        <v>664115000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>26115000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>8457000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №15/26</t>
+          <t>Shartnoma №185/26 bo'yicha oldindan t'lov</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>110899000</v>
+        <v>672572000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>40061000</v>
+        <v>15213000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7229</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>70838000</v>
+        <v>657359000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>58660000</v>
+        <v>276695000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Navoiy Mehmonxona MChJ</t>
+          <t>Chust Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>299507777</t>
+          <t>231937806</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000210026236001</t>
+          <t>20208000819152950001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №73/26</t>
+          <t>Оплата за сырье по договору №194/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>12178000</v>
+        <v>380664000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>121498000</v>
+        <v>5726000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Marg'ilon Mato XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>307201695</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000447921133001</t>
+          <t>20208000427440373001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №229/26 от 17.08.2026, НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>-109320000</v>
+        <v>374938000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>74490000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>51349000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bekobod Avto Savdo MChJ</t>
+          <t>Afrosiyob Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>390329013</t>
+          <t>377315002</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000643988360001</t>
+          <t>20208000258561180001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4341,37 +4341,37 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9881 от 19.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2850</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>-34830000</v>
+        <v>323589000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>24881000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>83848000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4381,451 +4381,446 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №247/26 от 21.08.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №222/26</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>-9949000</v>
+        <v>239741000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>11407000</v>
+        <v>19140000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №197/26 от 24.08.2026</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №56/26 ОТ 27.08.2026</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1458000</v>
+        <v>258881000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>10143000</v>
+        <v>15458000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5824 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4321 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>11601000</v>
+        <v>274339000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>5726000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>8295000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000760984131001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №224</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>5875000</v>
+        <v>282634000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>15106000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>17897000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №8830 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>-9231000</v>
+        <v>300531000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>24306000</v>
+        <v>50316000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bekobod Avto Savdo MChJ</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>390329013</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000643988360001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №52/26 от 25.08.2026</t>
+          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>15075000</v>
+        <v>350847000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>15904000</v>
+        <v>26189000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SHARTNOMA №80/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Предоплата за товар по договору №40/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>30979000</v>
+        <v>377036000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>23728000</v>
+        <v>17316000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3422 от 26.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №380</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>54707000</v>
+        <v>394352000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>25397000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>10044000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №186/26 от 26.08.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2636 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>29310000</v>
+        <v>404396000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>55394000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>8861000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7067</t>
+          <t>Оплата за продукцию по договору №65/26, НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>-26084000</v>
+        <v>413257000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>25241000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>7666000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Bog'ishamol Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>291382543</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000977710952001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7947</t>
+          <t>Оплата по счет-фактуре №655 за поставленный товар</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>-51325000</v>
+        <v>420923000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>355215000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>206562717</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7290 28.08.2026, QQS bilan</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>303890000</v>
+        <v>420623000</v>
       </c>
     </row>
     <row r="116">
@@ -4836,17 +4831,22 @@
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>300000</v>
+        <v>24683000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4856,157 +4856,157 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Tovarlar uchun to'lov h/f №2394</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>303590000</v>
+        <v>395940000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>124972000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>37891000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8890 01.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №247/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>428562000</v>
+        <v>358049000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>61941000</v>
+        <v>75616000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Chirchiq Metall AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>352334616</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000059266073001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1673</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №80/26</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>366621000</v>
+        <v>282433000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>43122000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>20582000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Afrosiyob Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>377315002</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000258561180001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №198/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №9821</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>409743000</v>
+        <v>261851000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>29280000</v>
+        <v>91884000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5016,77 +5016,77 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8765</t>
+          <t>Оплата за сырье по договору №143/26 от 01.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>380463000</v>
+        <v>169967000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>9206000</v>
+        <v>104447000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №297</t>
+          <t>Оплата по счет-фактуре №6687 за поставленный товар</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>389669000</v>
+        <v>274414000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>11029000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>28612000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Nukus Polimer MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5096,37 +5096,37 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №2/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>400698000</v>
+        <v>245802000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>5536000</v>
+        <v>19478000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5136,112 +5136,112 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2288 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №3513 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>406234000</v>
+        <v>265280000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>61200000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>17555000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6498)</t>
+          <t>Saodat Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>16307000285424850417</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6498 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за товар по договору №93/26 от 03.09.2026</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>345034000</v>
+        <v>282835000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>29899000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>13644000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №42/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №146/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>374933000</v>
+        <v>269191000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>22592000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>61200000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>247726471</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6498)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>16307000285424850417</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5251,11 +5251,11 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3197 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6498 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>397525000</v>
+        <v>207991000</v>
       </c>
     </row>
     <row r="127">
@@ -5267,35 +5267,35 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>11533000</v>
+        <v>30743000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5074 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №4862 за поставленный товар</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>409058000</v>
+        <v>238734000</v>
       </c>
     </row>
     <row r="128">
@@ -5305,23 +5305,23 @@
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>9546000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>26493000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>267482320</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000975515929001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5331,11 +5331,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №72/25</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6681</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>399512000</v>
+        <v>265227000</v>
       </c>
     </row>
     <row r="129">
@@ -5345,37 +5345,37 @@
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>22257000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>12610000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Marg'ilon Mato XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>307201695</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000447921133001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №123/26</t>
+          <t>Оплата за продукцию по договору №211/26, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>377255000</v>
+        <v>277837000</v>
       </c>
     </row>
     <row r="130">
@@ -5385,58 +5385,63 @@
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>85826000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>8860000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Saodat Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №7986</t>
+          <t>Предоплата за товар по договору №121/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>291429000</v>
+        <v>286697000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>34002000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>24066000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bekobod Avto Savdo MChJ</t>
+          <t>Afrosiyob Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>390329013</t>
+          <t>377315002</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000643988360001</t>
+          <t>20208000258561180001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5446,77 +5451,72 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №217/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №123/26</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>325431000</v>
+        <v>262631000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>33206000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>85826000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>206562717</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №4/26 bo'yicha oldindan to'lov</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №1856</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>358637000</v>
+        <v>176805000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>12369000</v>
+        <v>27811000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5526,91 +5526,91 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4774 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №7230 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>371006000</v>
+        <v>204616000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>174233000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>9546000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>254594097</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000471190172001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9891 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №33/25</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>545239000</v>
+        <v>195070000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>34487000</v>
+        <v>14945000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №213/26, НДС 12%</t>
+          <t>Shartnoma №71/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>579726000</v>
+        <v>210015000</v>
       </c>
     </row>
     <row r="136">
@@ -5620,77 +5620,77 @@
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>30254000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>19863000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Farovon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>282320397</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000515929176001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №177/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №144/26</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>609980000</v>
+        <v>190152000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>21045000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>8612000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Saodat Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>372647110</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000964393583001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №131/26</t>
+          <t>Оплата за продукцию по дог. №190/26, НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>588935000</v>
+        <v>198764000</v>
       </c>
     </row>
     <row r="138">
@@ -5700,23 +5700,23 @@
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>13444000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>19904000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Chust Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>231937806</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000819152950001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5726,91 +5726,91 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3280 за поставленный товар</t>
+          <t>Оплата за сырье по договору №44/26 от 11.09.026, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>602379000</v>
+        <v>178860000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>9464000</v>
+        <v>10853000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №111/26 от 11.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №4147 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>611843000</v>
+        <v>189713000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>6996000</v>
+        <v>9140000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №38/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №102/26, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>618839000</v>
+        <v>198853000</v>
       </c>
     </row>
     <row r="141">
@@ -5820,37 +5820,37 @@
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>35165000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>11703000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6538 за поставленный товар</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>654004000</v>
+        <v>187150000</v>
       </c>
     </row>
     <row r="142">
@@ -5860,37 +5860,37 @@
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>34243000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>11703000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №1/26 от 14.09.2026</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>688247000</v>
+        <v>175447000</v>
       </c>
     </row>
     <row r="143">
@@ -5900,77 +5900,77 @@
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>18016000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>26471000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Nukus Polimer MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №254/26 от 14.09.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №43/26</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>706263000</v>
+        <v>148976000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>7984000</v>
+        <v>25644000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №249/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №139/26 от 15.09.2026</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>714247000</v>
+        <v>174620000</v>
       </c>
     </row>
     <row r="145">
@@ -5980,157 +5980,157 @@
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>8873000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>36260000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №63/26 от 15.09.2026</t>
+          <t>Оплата за товары согласно с/ф №38</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>723120000</v>
+        <v>138360000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>5506000</v>
+        <v>82495000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Omad Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>349173772</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000412269869001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5168 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по с/ф №4311 от 16.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>728626000</v>
+        <v>220855000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>12367000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>20605000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №23/26 от 15.09.2026, НДС 12%</t>
+          <t>Оплата за товар о с/ф №155 от 16.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>716259000</v>
+        <v>241460000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>330403000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>13963000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №84/26</t>
+          <t>Предоплата за товар по дог. №32/26 от 16.09.2026</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>385856000</v>
+        <v>255423000</v>
       </c>
     </row>
     <row r="149">
@@ -6140,37 +6140,37 @@
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>11703000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>9394000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата по с/ф №7908 за поставленный товар</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>374153000</v>
+        <v>264817000</v>
       </c>
     </row>
     <row r="150">
@@ -6181,236 +6181,236 @@
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>11703000</v>
+        <v>53372000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad soligi avgust 2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №6122</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>362450000</v>
+        <v>211445000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>25883000</v>
+        <v>17616000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9738 от 17.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №174/26, QQS 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>388333000</v>
+        <v>229061000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>11753000</v>
+        <v>16855000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №35 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №143/26, НДС 12%</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>400086000</v>
+        <v>245916000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>8218000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>15612000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №126/26, НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>408304000</v>
+        <v>230304000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>21637000</v>
+        <v>16384000</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
+          <t>Afrosiyob Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>363744948</t>
+          <t>377315002</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>20208000258561180001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №73/26</t>
+          <t>Предоплата за материалы по договору №192/26</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>386667000</v>
+        <v>213920000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>108487000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>33753000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №70/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №108/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>495154000</v>
+        <v>180167000</v>
       </c>
     </row>
     <row r="156">
@@ -6420,23 +6420,23 @@
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>18892000</v>
-      </c>
+      <c r="C156" s="2" t="n">
+        <v>56539000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Nukus Polimer MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>320169544</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000792113350001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6446,37 +6446,37 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9963 за поставленный товар</t>
+          <t>Оплата за сырье по договору №286/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>514046000</v>
+        <v>123628000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>15185000</v>
+        <v>670929000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ilhom Tekstil XK</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>296526989</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000107535285001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6486,157 +6486,157 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9188 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №104/26, НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>529231000</v>
+        <v>794557000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>13796000</v>
+        <v>19217000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №63/26 от 21.09.2026</t>
+          <t>Оплата за товар по с/ф №6571 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>543027000</v>
+        <v>813774000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>12153000</v>
+        <v>50028000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №3175 за поставленный товар</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>555180000</v>
+        <v>863802000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>10099000</v>
+        <v>28181000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Zafar Metall MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>247726471</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000069643935001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7187 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №148/26, НДС 12%</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>565279000</v>
+        <v>891983000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>27920000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>24005000</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Meva-Sabzavot MChJ</t>
+          <t>Nurafshon Agro AJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>222913825</t>
+          <t>232901386</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000399777109001</t>
+          <t>20208000398836004001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6646,317 +6646,312 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6170</t>
+          <t>Оплата за товар по счет-фактуре №9210 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>537359000</v>
+        <v>915988000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>34562000</v>
-      </c>
+      <c r="C162" s="2" t="n">
+        <v>5967000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000427440373001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7210 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>571921000</v>
+        <v>910021000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>12317000</v>
-      </c>
+      <c r="C163" s="2" t="n">
+        <v>30951000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №57/26 от 22.09.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №272/26, QQS bilan</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>584238000</v>
+        <v>879070000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>15257000</v>
+        <v>122132000</v>
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Оплата за товары согласно с/ф №1228</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>568981000</v>
+        <v>756938000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>19445000</v>
-      </c>
+      <c r="C165" s="2" t="n">
+        <v>46794000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №16/26</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>588426000</v>
+        <v>710144000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>10028000</v>
+        <v>88553000</v>
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Shodlik Sut MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>229576767</t>
+          <t>317431597</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000496055275001</t>
+          <t>20208000754459408001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №43/26</t>
+          <t>Оплата за сырье по договору №263/26 от 29.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>578398000</v>
+        <v>621591000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="n">
-        <v>10144000</v>
+        <v>18251000</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №200/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №845 за поставленный товар</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>588542000</v>
+        <v>639842000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
-      <c r="C168" s="2" t="n">
-        <v>5967000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>12242000</v>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Saodat Logistik MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>356271740</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000760984131001</t>
+          <t>20208000194972343001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за продукцию по дог. №45/26, НДС 12%</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>582575000</v>
+        <v>652084000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>91729000</v>
+        <v>300000</v>
       </c>
       <c r="D169" s="2" t="n"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>363744948</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000937568230001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6966,511 +6961,76 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №513</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>490846000</v>
+        <v>651784000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>109122000</v>
-      </c>
+      <c r="C170" s="2" t="n">
+        <v>353484000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Farovon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>206562717</t>
+          <t>282320397</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000031949723001</t>
+          <t>20208000515929176001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8308 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №54/26</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>599968000</v>
+        <v>298300000</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>93193000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Sarbon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>380679719</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000922239935001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №166/26</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>506775000</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>3836738000</v>
+      </c>
+      <c r="D171" s="4" t="n">
+        <v>3880538000</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>28747000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>206562717</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000031949723001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №803 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>535522000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>8474000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>206562717</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000031949723001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9537 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>543996000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>7466000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>206562717</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000031949723001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №16/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>551462000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>13003000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>363744948</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000937568230001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №6122</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>538459000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>8268000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Navoiy Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>299507777</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000210026236001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №52/26</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>530191000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>81176000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Saodat Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>315491737</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000264122698001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №255/26 ОТ 30.09.2026</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>611367000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n">
-        <v>19388000</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Shodlik Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>206562717</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000031949723001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №94/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>630755000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Navbahor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>BANK XIZMATI UCHUN KOMISSIYA</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>630455000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>126130000</v>
-      </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>363744948</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000937568230001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №6407</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>504325000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>206025000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Omad Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>363744948</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000937568230001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №1798</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
         <v>298300000</v>
       </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="n">
-        <v>3812499000</v>
-      </c>
-      <c r="D182" s="4" t="n">
-        <v>3856299000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="n">
-        <v>298300000</v>
-      </c>
-      <c r="D183" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
